--- a/docs/AVSAR_Project_Timeline_v1.0.xlsx
+++ b/docs/AVSAR_Project_Timeline_v1.0.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Sixteen-table schema; declare every legal state transition in one module; design the eligibility gate so each check cites its rule.</t>
+          <t>Seventeen-table schema; declare every legal state transition in one module; design the eligibility gate so each check cites its rule.</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Seven role-aware workspaces across twenty-four routes: authoring, discovery, scoring, pilot monitoring, procurement, payments, grievance, audit and administration.</t>
+          <t>Seven role-aware workspaces across thirty-one routes: authoring, discovery, scoring, pilot monitoring, procurement, payments, grievance, audit and administration.</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
